--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97601</v>
+        <v>97604</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97604</v>
+        <v>97633</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97633</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>97646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97646</v>
+        <v>97651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97655</v>
+        <v>97657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40214-2025 artfynd.xlsx
+++ b/artfynd/A 40214-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129519414</v>
       </c>
       <c r="B2" t="n">
-        <v>97657</v>
+        <v>97667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
